--- a/giro_da_praça_ofertas - TERÇA E QUARTA.xlsx
+++ b/giro_da_praça_ofertas - TERÇA E QUARTA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E122033-25E2-47E4-B043-92417340BCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB6A5B1-79F3-4B04-88CE-588B2A3A9BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -272,38 +272,43 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="7"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -353,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -361,16 +366,25 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -379,16 +393,11 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,773 +704,773 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>100031</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="10">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>24.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="3" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="9">
         <v>199440</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="11">
+      <c r="E3" s="11"/>
+      <c r="F3" s="12">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="9">
         <v>167687</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="11">
+      <c r="E4" s="11"/>
+      <c r="F4" s="12">
         <v>9.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>100054</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="10">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>8.59</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>343925</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="10">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>6.49</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="9">
         <v>318330</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="11">
+      <c r="E8" s="11"/>
+      <c r="F8" s="12">
         <v>12.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>174298</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="10">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="s">
+    <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="9">
         <v>189503</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="11">
+      <c r="E10" s="11"/>
+      <c r="F10" s="12">
         <v>6.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="5" t="s">
+    <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="9">
         <v>257157</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="11">
+      <c r="E11" s="11"/>
+      <c r="F11" s="12">
         <v>8.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="5" t="s">
+    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="9">
         <v>338763</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="11">
+      <c r="E12" s="11"/>
+      <c r="F12" s="12">
         <v>25.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="5" t="s">
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="9">
         <v>273714</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="11">
+      <c r="E13" s="11"/>
+      <c r="F13" s="12">
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>336565</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="10">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>7.19</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="5" t="s">
+    <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="9">
         <v>101728</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="11">
+      <c r="E15" s="11"/>
+      <c r="F15" s="12">
         <v>12.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="5" t="s">
+    <row r="16" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="9">
         <v>321107</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="11">
+      <c r="E16" s="11"/>
+      <c r="F16" s="12">
         <v>2.19</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="5" t="s">
+    <row r="17" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="9">
         <v>100876</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="11">
+      <c r="E17" s="11"/>
+      <c r="F17" s="12">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>106961</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="10">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>107640</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="10">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>3.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="5" t="s">
+    <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="9">
         <v>100705</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="11">
+      <c r="E20" s="11"/>
+      <c r="F20" s="12">
         <v>6.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="5" t="s">
+    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="9">
         <v>100024</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="11">
+      <c r="E21" s="11"/>
+      <c r="F21" s="12">
         <v>5.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="5" t="s">
+    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="9">
         <v>100120</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="11">
+      <c r="E22" s="11"/>
+      <c r="F22" s="12">
         <v>2.39</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>101063</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="10">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>3.59</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="5" t="s">
+    <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="9">
         <v>101083</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="11">
+      <c r="E24" s="11"/>
+      <c r="F24" s="12">
         <v>7.69</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>142446</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="10">
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
         <v>7.19</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>307145</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="10">
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="5" t="s">
+    <row r="27" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="9">
         <v>131884</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="11">
+      <c r="E27" s="11"/>
+      <c r="F27" s="12">
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="5" t="s">
+    <row r="28" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="9">
         <v>106791</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="11">
+      <c r="E28" s="11"/>
+      <c r="F28" s="12">
         <v>3.29</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="5" t="s">
+    <row r="30" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="9">
         <v>104406</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="11">
+      <c r="E30" s="11"/>
+      <c r="F30" s="12">
         <v>10.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="5" t="s">
+    <row r="31" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="9">
         <v>104410</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="11">
+      <c r="E31" s="11"/>
+      <c r="F31" s="12">
         <v>9.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="5" t="s">
+    <row r="32" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="9">
         <v>102282</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="11">
+      <c r="E32" s="11"/>
+      <c r="F32" s="12">
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="5" t="s">
+    <row r="33" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="9">
         <v>264452</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="11">
+      <c r="E33" s="11"/>
+      <c r="F33" s="12">
         <v>5.49</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="5" t="s">
+    <row r="34" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="9">
         <v>288739</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="11">
+      <c r="E34" s="11"/>
+      <c r="F34" s="12">
         <v>7.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="6">
         <v>341231</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="10">
+      <c r="E35" s="7"/>
+      <c r="F35" s="8">
         <f>15*3.19</f>
         <v>47.85</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="6">
         <v>324556</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="10">
+      <c r="E36" s="7"/>
+      <c r="F36" s="8">
         <f>15*2.99</f>
         <v>44.85</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="5" t="s">
+    <row r="37" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="9">
         <v>102085</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="11">
+      <c r="E37" s="11"/>
+      <c r="F37" s="12">
         <v>13.99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="5" t="s">
+    <row r="38" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="9">
         <v>109726</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="11">
+      <c r="E38" s="11"/>
+      <c r="F38" s="12">
         <v>289.99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="5" t="s">
+    <row r="40" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="9">
         <v>100431</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="11">
+      <c r="E40" s="11"/>
+      <c r="F40" s="12">
         <v>11.39</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="5" t="s">
+    <row r="41" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="9">
         <v>106712</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="11">
+      <c r="E41" s="11"/>
+      <c r="F41" s="12">
         <v>12.99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="5" t="s">
+    <row r="42" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="9">
         <v>279798</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="11">
+      <c r="E42" s="11"/>
+      <c r="F42" s="12">
         <v>10.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="6">
         <v>119826</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="10">
+      <c r="E43" s="7"/>
+      <c r="F43" s="8">
         <v>2.59</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="5" t="s">
+    <row r="44" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="9">
         <v>204689</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="11">
+      <c r="E44" s="11"/>
+      <c r="F44" s="12">
         <v>2.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="5" t="s">
+    <row r="45" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="9">
         <v>259568</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="11">
+      <c r="E45" s="11"/>
+      <c r="F45" s="12">
         <v>11.99</v>
       </c>
     </row>
